--- a/templates/collaborator_checklist_template.xlsx
+++ b/templates/collaborator_checklist_template.xlsx
@@ -1,136 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nam Nguyen Hoai\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA82B3A-09E7-475C-894D-C2EE13494C5C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{BEDE0D0B-8FC2-4A41-A119-F0856454F792}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="HROS30.06" sheetId="1" r:id="rId1"/>
+    <sheet name="HROS30.06" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>Mã nhân viên</t>
-  </si>
-  <si>
-    <t>Họ tên</t>
-  </si>
-  <si>
-    <t>Mã số thuế</t>
-  </si>
-  <si>
-    <t>Ngày sinh</t>
-  </si>
-  <si>
-    <t>Số CCCD</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Số điện thoại</t>
-  </si>
-  <si>
-    <t>Hồ sơ</t>
-  </si>
-  <si>
-    <t>Hợp đồng dịch vụ</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>CCCD</t>
-  </si>
-  <si>
-    <t>Bằng cấp</t>
-  </si>
-  <si>
-    <t>Cam kết thuế</t>
-  </si>
-  <si>
-    <t>Biên bản thanh lí</t>
-  </si>
-  <si>
-    <t>Thông tin cư trú</t>
-  </si>
-  <si>
-    <t>Địa chỉ</t>
-  </si>
-  <si>
-    <t>Ngày bắt đầu</t>
-  </si>
-  <si>
-    <t>Ngày kết thúc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy;@"/>
   </numFmts>
   <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -148,7 +61,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -226,72 +139,122 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{008EDA51-15F4-4CE2-B017-1D94D08CC5DC}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFEF9263"/>
-      <color rgb="FFF3AC89"/>
-    </mruColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -611,308 +574,326 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3194E1E-9B79-4A92-A2F3-3220A899756E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A2:Q30"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.1640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="22.75" customWidth="1"/>
-    <col min="4" max="4" width="15.1640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="12.4140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="26.4140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="14.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="60.4140625" customWidth="1"/>
-    <col min="10" max="11" width="22.5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="8.75" customWidth="1"/>
-    <col min="13" max="13" width="18.4140625" customWidth="1"/>
-    <col min="14" max="14" width="21.5" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="16.1640625" customWidth="1"/>
-    <col min="17" max="17" width="27.1640625" customWidth="1"/>
+    <col width="12.83203125" customWidth="1" min="1" max="1"/>
+    <col width="15.1640625" customWidth="1" style="3" min="2" max="2"/>
+    <col width="22.75" customWidth="1" min="3" max="3"/>
+    <col width="15.1640625" customWidth="1" style="3" min="4" max="4"/>
+    <col width="12.4140625" customWidth="1" style="3" min="5" max="5"/>
+    <col width="15.83203125" customWidth="1" style="3" min="6" max="6"/>
+    <col width="26.4140625" customWidth="1" style="3" min="7" max="7"/>
+    <col width="14.25" customWidth="1" style="3" min="8" max="8"/>
+    <col width="60.4140625" customWidth="1" min="9" max="9"/>
+    <col width="22.5" customWidth="1" style="3" min="10" max="11"/>
+    <col width="8.75" customWidth="1" min="12" max="12"/>
+    <col width="18.4140625" customWidth="1" min="13" max="13"/>
+    <col width="21.5" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="16.1640625" customWidth="1" min="16" max="16"/>
+    <col width="27.1640625" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" ht="15">
-      <c r="A2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-    </row>
-    <row r="3" spans="1:17" ht="15">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="14.15" customHeight="1">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-    </row>
-    <row r="5" spans="1:17" ht="15" customHeight="1">
-      <c r="B5" s="2"/>
-      <c r="E5" s="4"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="N5" s="5"/>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="B6" s="2"/>
-      <c r="E6" s="4"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="N6" s="5"/>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="B7" s="2"/>
-      <c r="E7" s="4"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="N7" s="5"/>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="B8" s="2"/>
-      <c r="E8" s="4"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="N8" s="5"/>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="B9" s="2"/>
-      <c r="E9" s="4"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="N9" s="5"/>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="B10" s="2"/>
-      <c r="E10" s="4"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="N10" s="5"/>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="B11" s="2"/>
-      <c r="E11" s="4"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="N11" s="5"/>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="B12" s="2"/>
-      <c r="E12" s="4"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="N12" s="5"/>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="B13" s="2"/>
-      <c r="E13" s="4"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="N13" s="5"/>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="B14" s="2"/>
-      <c r="E14" s="4"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="N14" s="5"/>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="E15" s="4"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="E16" s="4"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="5:14">
-      <c r="E17" s="4"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="N17" s="5"/>
-    </row>
-    <row r="18" spans="5:14">
-      <c r="E18" s="4"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="N18" s="5"/>
-    </row>
-    <row r="19" spans="5:14">
-      <c r="E19" s="4"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="N19" s="5"/>
-    </row>
-    <row r="20" spans="5:14">
-      <c r="E20" s="4"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="N20" s="5"/>
-    </row>
-    <row r="21" spans="5:14">
-      <c r="E21" s="4"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="N21" s="5"/>
-    </row>
-    <row r="22" spans="5:14">
-      <c r="E22" s="4"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="N22" s="5"/>
-    </row>
-    <row r="23" spans="5:14">
-      <c r="E23" s="4"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="N23" s="5"/>
-    </row>
-    <row r="24" spans="5:14">
-      <c r="E24" s="4"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="N24" s="5"/>
-    </row>
-    <row r="25" spans="5:14">
-      <c r="E25" s="4"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="N25" s="5"/>
-    </row>
-    <row r="26" spans="5:14">
-      <c r="E26" s="4"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="N26" s="5"/>
-    </row>
-    <row r="27" spans="5:14">
-      <c r="E27" s="4"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="N27" s="5"/>
-    </row>
-    <row r="28" spans="5:14">
-      <c r="E28" s="4"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="N28" s="5"/>
-    </row>
-    <row r="29" spans="5:14">
-      <c r="E29" s="4"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="N29" s="5"/>
-    </row>
-    <row r="30" spans="5:14">
-      <c r="E30" s="4"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="N30" s="5"/>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Mã nhân viên</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Họ tên</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Mã số thuế</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Ngày sinh</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Số CCCD</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Số điện thoại</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Địa chỉ</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Hồ sơ</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="14" t="n"/>
+      <c r="M2" s="14" t="n"/>
+      <c r="N2" s="19" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="15" t="n"/>
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="16" t="n"/>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>Hợp đồng dịch vụ</t>
+        </is>
+      </c>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>CCCD</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>Cam kết thuế</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>Biên bản thanh lí</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.15" customHeight="1">
+      <c r="A4" s="17" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
+      <c r="G4" s="17" t="n"/>
+      <c r="H4" s="17" t="n"/>
+      <c r="I4" s="18" t="n"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Ngày bắt đầu</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Ngày kết thúc</t>
+        </is>
+      </c>
+      <c r="L4" s="17" t="n"/>
+      <c r="M4" s="17" t="n"/>
+      <c r="N4" s="17" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="B5" s="2" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="E15" s="4" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="N15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="E16" s="4" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="N16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="E17" s="4" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="E18" s="4" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="E19" s="4" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="E20" s="4" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="E21" s="4" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="4" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="E23" s="4" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="E24" s="4" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="E25" s="4" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="E26" s="4" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="E27" s="4" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="E28" s="4" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="E29" s="4" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="4" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="14">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="A2:A4"/>
     <mergeCell ref="L3:L4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="J3:K3"/>
     <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="J2:Q2"/>
-    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="E2:E4"/>
-    <mergeCell ref="F2:F4"/>
-    <mergeCell ref="G2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="I2:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/templates/collaborator_checklist_template.xlsx
+++ b/templates/collaborator_checklist_template.xlsx
@@ -1,49 +1,111 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programme\git_repository\bmk\bmk-ctv-service\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DB3D69-72CD-4FF2-9164-C6EEF4A5D3A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="HROS30.06" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="HROS30.06" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Mã nhân viên</t>
+  </si>
+  <si>
+    <t>Họ tên</t>
+  </si>
+  <si>
+    <t>Mã số thuế</t>
+  </si>
+  <si>
+    <t>Ngày sinh</t>
+  </si>
+  <si>
+    <t>Số CCCD</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Số điện thoại</t>
+  </si>
+  <si>
+    <t>Địa chỉ</t>
+  </si>
+  <si>
+    <t>Hồ sơ</t>
+  </si>
+  <si>
+    <t>Hợp đồng dịch vụ</t>
+  </si>
+  <si>
+    <t>CCCD</t>
+  </si>
+  <si>
+    <t>Cam kết thuế</t>
+  </si>
+  <si>
+    <t>Biên bản thanh lí</t>
+  </si>
+  <si>
+    <t>Ngày bắt đầu</t>
+  </si>
+  <si>
+    <t>Ngày kết thúc</t>
+  </si>
+  <si>
+    <t>Người bàn giao</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy;@"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -61,7 +123,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -113,17 +175,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -143,15 +194,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -174,15 +216,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -196,65 +229,61 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -574,317 +603,282 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A2:Q30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:O30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="12.83203125" customWidth="1" min="1" max="1"/>
-    <col width="15.1640625" customWidth="1" style="3" min="2" max="2"/>
-    <col width="22.75" customWidth="1" min="3" max="3"/>
-    <col width="15.1640625" customWidth="1" style="3" min="4" max="4"/>
-    <col width="12.4140625" customWidth="1" style="3" min="5" max="5"/>
-    <col width="15.83203125" customWidth="1" style="3" min="6" max="6"/>
-    <col width="26.4140625" customWidth="1" style="3" min="7" max="7"/>
-    <col width="14.25" customWidth="1" style="3" min="8" max="8"/>
-    <col width="60.4140625" customWidth="1" min="9" max="9"/>
-    <col width="22.5" customWidth="1" style="3" min="10" max="11"/>
-    <col width="8.75" customWidth="1" min="12" max="12"/>
-    <col width="18.4140625" customWidth="1" min="13" max="13"/>
-    <col width="21.5" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="16.1640625" customWidth="1" min="16" max="16"/>
-    <col width="27.1640625" customWidth="1" min="17" max="17"/>
+    <col min="1" max="1" width="12.81640625" customWidth="1"/>
+    <col min="2" max="2" width="15.1796875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.81640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="26.453125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14.26953125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="60.453125" customWidth="1"/>
+    <col min="10" max="11" width="22.453125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" customWidth="1"/>
+    <col min="13" max="13" width="18.453125" customWidth="1"/>
+    <col min="14" max="14" width="21.453125" customWidth="1"/>
+    <col min="15" max="15" width="29.54296875" customWidth="1"/>
+    <col min="16" max="16" width="16.1796875" customWidth="1"/>
+    <col min="17" max="17" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>Mã nhân viên</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>Họ tên</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>Mã số thuế</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>Ngày sinh</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>Số CCCD</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Số điện thoại</t>
-        </is>
-      </c>
-      <c r="I2" s="13" t="inlineStr">
-        <is>
-          <t>Địa chỉ</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Hồ sơ</t>
-        </is>
-      </c>
-      <c r="K2" s="14" t="n"/>
-      <c r="L2" s="14" t="n"/>
-      <c r="M2" s="14" t="n"/>
-      <c r="N2" s="19" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="15" t="n"/>
-      <c r="B3" s="15" t="n"/>
-      <c r="C3" s="15" t="n"/>
-      <c r="D3" s="15" t="n"/>
-      <c r="E3" s="15" t="n"/>
-      <c r="F3" s="15" t="n"/>
-      <c r="G3" s="15" t="n"/>
-      <c r="H3" s="15" t="n"/>
-      <c r="I3" s="16" t="n"/>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>Hợp đồng dịch vụ</t>
-        </is>
-      </c>
-      <c r="K3" s="14" t="n"/>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>CCCD</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
-        <is>
-          <t>Cam kết thuế</t>
-        </is>
-      </c>
-      <c r="N3" s="6" t="inlineStr">
-        <is>
-          <t>Biên bản thanh lí</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="14.15" customHeight="1">
-      <c r="A4" s="17" t="n"/>
-      <c r="B4" s="17" t="n"/>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="17" t="n"/>
-      <c r="E4" s="17" t="n"/>
-      <c r="F4" s="17" t="n"/>
-      <c r="G4" s="17" t="n"/>
-      <c r="H4" s="17" t="n"/>
-      <c r="I4" s="18" t="n"/>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Ngày bắt đầu</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>Ngày kết thúc</t>
-        </is>
-      </c>
-      <c r="L4" s="17" t="n"/>
-      <c r="M4" s="17" t="n"/>
-      <c r="N4" s="17" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="2" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="2" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="2" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="2" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="2" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="2" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="2" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="2" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="2" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-    </row>
-    <row r="15">
-      <c r="E15" s="4" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="N15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="E16" s="4" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="N16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="E17" s="4" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-    </row>
-    <row r="18">
-      <c r="E18" s="4" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="E19" s="4" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-    </row>
-    <row r="20">
-      <c r="E20" s="4" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="E21" s="4" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="E22" s="4" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-    </row>
-    <row r="23">
-      <c r="E23" s="4" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-    </row>
-    <row r="24">
-      <c r="E24" s="4" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-    </row>
-    <row r="25">
-      <c r="E25" s="4" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="E26" s="4" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="E27" s="4" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-    </row>
-    <row r="28">
-      <c r="E28" s="4" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-    </row>
-    <row r="29">
-      <c r="E29" s="4" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="N29" s="5" t="n"/>
-    </row>
-    <row r="30">
-      <c r="E30" s="4" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="N30" s="5" t="n"/>
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="14"/>
+      <c r="L3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" s="7"/>
+    </row>
+    <row r="4" spans="1:15" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="8"/>
+    </row>
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="2"/>
+      <c r="E5" s="4"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="N5" s="5"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="2"/>
+      <c r="E6" s="4"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="N6" s="5"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="2"/>
+      <c r="E7" s="4"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="N7" s="5"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="2"/>
+      <c r="E8" s="4"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="N8" s="5"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B9" s="2"/>
+      <c r="E9" s="4"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="N9" s="5"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="2"/>
+      <c r="E10" s="4"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="N10" s="5"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="2"/>
+      <c r="E11" s="4"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="N11" s="5"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B12" s="2"/>
+      <c r="E12" s="4"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="N12" s="5"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="2"/>
+      <c r="E13" s="4"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="N13" s="5"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="2"/>
+      <c r="E14" s="4"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="N14" s="5"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="E15" s="4"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="E16" s="4"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E17" s="4"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="N17" s="5"/>
+    </row>
+    <row r="18" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E18" s="4"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="N18" s="5"/>
+    </row>
+    <row r="19" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E19" s="4"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="N19" s="5"/>
+    </row>
+    <row r="20" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E20" s="4"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="N20" s="5"/>
+    </row>
+    <row r="21" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E21" s="4"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="N21" s="5"/>
+    </row>
+    <row r="22" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E22" s="4"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="N22" s="5"/>
+    </row>
+    <row r="23" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E23" s="4"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="N23" s="5"/>
+    </row>
+    <row r="24" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E24" s="4"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="N24" s="5"/>
+    </row>
+    <row r="25" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E25" s="4"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="N25" s="5"/>
+    </row>
+    <row r="26" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E26" s="4"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="N26" s="5"/>
+    </row>
+    <row r="27" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E27" s="4"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="N27" s="5"/>
+    </row>
+    <row r="28" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E28" s="4"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="N28" s="5"/>
+    </row>
+    <row r="29" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E29" s="4"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="N29" s="5"/>
+    </row>
+    <row r="30" spans="5:14" x14ac:dyDescent="0.35">
+      <c r="E30" s="4"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="N30" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="G2:G4"/>
+  <mergeCells count="15">
+    <mergeCell ref="O2:O4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="D2:D4"/>
@@ -894,6 +888,11 @@
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="E2:E4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="G2:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/templates/collaborator_checklist_template.xlsx
+++ b/templates/collaborator_checklist_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programme\git_repository\bmk\bmk-ctv-service\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94DB3D69-72CD-4FF2-9164-C6EEF4A5D3A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119779F7-2892-4BED-B906-CB83609A5431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>STT</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>Người bàn giao</t>
+  </si>
+  <si>
+    <t>Ngày bàn giao</t>
   </si>
 </sst>
 </file>
@@ -234,7 +237,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -256,19 +259,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -604,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:O30"/>
+  <dimension ref="A2:P30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.81640625" customWidth="1"/>
@@ -621,39 +630,39 @@
     <col min="13" max="13" width="18.453125" customWidth="1"/>
     <col min="14" max="14" width="21.453125" customWidth="1"/>
     <col min="15" max="15" width="29.54296875" customWidth="1"/>
-    <col min="16" max="16" width="16.1796875" customWidth="1"/>
+    <col min="16" max="16" width="20.54296875" style="19" customWidth="1"/>
     <col min="17" max="17" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="11" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="9" t="s">
         <v>9</v>
       </c>
       <c r="K2" s="14"/>
@@ -663,41 +672,45 @@
       <c r="O2" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
+      <c r="P2" s="16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
       <c r="I3" s="7"/>
       <c r="J3" s="13" t="s">
         <v>10</v>
       </c>
       <c r="K3" s="14"/>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="9" t="s">
         <v>13</v>
       </c>
       <c r="O3" s="7"/>
-    </row>
-    <row r="4" spans="1:15" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
+      <c r="P3" s="17"/>
+    </row>
+    <row r="4" spans="1:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
       <c r="I4" s="8"/>
       <c r="J4" s="1" t="s">
         <v>14</v>
@@ -705,88 +718,90 @@
       <c r="K4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
       <c r="O4" s="8"/>
-    </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P4" s="18"/>
+    </row>
+    <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="2"/>
       <c r="E5" s="4"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="N5" s="5"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P5" s="5"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B6" s="2"/>
       <c r="E6" s="4"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B7" s="2"/>
       <c r="E7" s="4"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
       <c r="N7" s="5"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B8" s="2"/>
       <c r="E8" s="4"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="N8" s="5"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B9" s="2"/>
       <c r="E9" s="4"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="N9" s="5"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B10" s="2"/>
       <c r="E10" s="4"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="N10" s="5"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B11" s="2"/>
       <c r="E11" s="4"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
       <c r="N11" s="5"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B12" s="2"/>
       <c r="E12" s="4"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
       <c r="N12" s="5"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B13" s="2"/>
       <c r="E13" s="4"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B14" s="2"/>
       <c r="E14" s="4"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="N14" s="5"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="E15" s="4"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="E16" s="4"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -877,7 +892,12 @@
       <c r="N30" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="P2:P4"/>
     <mergeCell ref="O2:O4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="B2:B4"/>
@@ -889,10 +909,6 @@
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="I2:I4"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="G2:G4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/templates/collaborator_checklist_template.xlsx
+++ b/templates/collaborator_checklist_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programme\git_repository\bmk\bmk-ctv-service\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119779F7-2892-4BED-B906-CB83609A5431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5CE54B-F778-45DA-AB08-B71E91CF806D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>STT</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Ngày bàn giao</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
   </si>
 </sst>
 </file>
@@ -254,30 +257,30 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -613,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:P30"/>
+  <dimension ref="A2:Q30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.81640625" customWidth="1"/>
@@ -630,101 +633,106 @@
     <col min="13" max="13" width="18.453125" customWidth="1"/>
     <col min="14" max="14" width="21.453125" customWidth="1"/>
     <col min="15" max="15" width="29.54296875" customWidth="1"/>
-    <col min="16" max="16" width="20.54296875" style="19" customWidth="1"/>
+    <col min="16" max="16" width="20.54296875" style="6" customWidth="1"/>
     <col min="17" max="17" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="6" t="s">
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="P2" s="11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="13" t="s">
+      <c r="Q2" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="9" t="s">
+      <c r="K3" s="18"/>
+      <c r="L3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="7"/>
-      <c r="P3" s="17"/>
-    </row>
-    <row r="4" spans="1:16" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="8"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+    </row>
+    <row r="4" spans="1:17" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="16"/>
       <c r="J4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="18"/>
-    </row>
-    <row r="5" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+    </row>
+    <row r="5" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="2"/>
       <c r="E5" s="4"/>
       <c r="J5" s="5"/>
@@ -732,76 +740,76 @@
       <c r="N5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B6" s="2"/>
       <c r="E6" s="4"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B7" s="2"/>
       <c r="E7" s="4"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
       <c r="N7" s="5"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B8" s="2"/>
       <c r="E8" s="4"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="N8" s="5"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B9" s="2"/>
       <c r="E9" s="4"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="N9" s="5"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B10" s="2"/>
       <c r="E10" s="4"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="N10" s="5"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B11" s="2"/>
       <c r="E11" s="4"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
       <c r="N11" s="5"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B12" s="2"/>
       <c r="E12" s="4"/>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
       <c r="N12" s="5"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B13" s="2"/>
       <c r="E13" s="4"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B14" s="2"/>
       <c r="E14" s="4"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="N14" s="5"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E15" s="4"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E16" s="4"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -892,7 +900,8 @@
       <c r="N30" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="Q2:Q4"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="C2:C4"/>
